--- a/latest/BoM/Positional/pedalboard-hw-bom.xlsx
+++ b/latest/BoM/Positional/pedalboard-hw-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="580">
   <si>
     <t>Row</t>
   </si>
@@ -394,9 +394,6 @@
     <t>LED_SMD</t>
   </si>
   <si>
-    <t>~</t>
-  </si>
-  <si>
     <t>https://www.digikey.ch/en/products/detail/harvatek-corporation/B1701URO-20D000114U1930/16671739</t>
   </si>
   <si>
@@ -730,9 +727,6 @@
     <t>https://www.molex.com/en-us/products/part-detail/676433910?display=pdf</t>
   </si>
   <si>
-    <t>https://www.digikey.ch/de/products/detail/molex/0676433910/3598521</t>
-  </si>
-  <si>
     <t>35.0744</t>
   </si>
   <si>
@@ -763,9 +757,6 @@
     <t>https://cdn.amphenol-cs.com/media/wysiwyg/files/drawing/10103594.pdf</t>
   </si>
   <si>
-    <t>https://www.digikey.ch/de/products/detail/amphenol-cs-fci/10103594-0001LF/2350351</t>
-  </si>
-  <si>
     <t>2.6644</t>
   </si>
   <si>
@@ -1153,541 +1144,541 @@
     <t>87.4944</t>
   </si>
   <si>
-    <t>2.5500</t>
+    <t>2.7000</t>
+  </si>
+  <si>
+    <t>1.6500</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>AP2553W6</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/AP255x.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/en/products/detail/AP2553W6-7/AP2553W6-7DICT-ND/3882112</t>
+  </si>
+  <si>
+    <t>55.0870</t>
+  </si>
+  <si>
+    <t>79.1174</t>
+  </si>
+  <si>
+    <t>3.6000</t>
+  </si>
+  <si>
+    <t>2.5000</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>AP64351</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>AP64501SP-13</t>
+  </si>
+  <si>
+    <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.71x3.4mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/AP64501.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AP64501SP-13/10419715</t>
+  </si>
+  <si>
+    <t>141.5144</t>
+  </si>
+  <si>
+    <t>88.5944</t>
+  </si>
+  <si>
+    <t>6.9000</t>
+  </si>
+  <si>
+    <t>4.9000</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>I2C Serial EEPROM, 1Kb (128x8) with Unique Serial Number, SOT-23-5</t>
+  </si>
+  <si>
+    <t>AT24CS01-STUM</t>
+  </si>
+  <si>
+    <t>Memory_EEPROM</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>http://ww1.microchip.com/downloads/en/DeviceDoc/Atmel-8815-SEEPROM-AT24CS01-02-Datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/microchip-technology/AT24CS01-STUM-T/3973063</t>
+  </si>
+  <si>
+    <t>127.9944</t>
+  </si>
+  <si>
+    <t>86.4944</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Low-Power, Two-Port, High-Speed, USB2.0 (480Mbps) or UART Switch, MSOP-10</t>
+  </si>
+  <si>
+    <t>FSUSB42MUX</t>
+  </si>
+  <si>
+    <t>Interface_USB</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>TSSOP-10_3x3mm_P0.5mm</t>
+  </si>
+  <si>
+    <t>Package_SO</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pub/Collateral/FSUSB42-D.PDF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/onsemi/FSUSB42MUX/2036916</t>
+  </si>
+  <si>
+    <t>38.1144</t>
+  </si>
+  <si>
+    <t>73.8844</t>
+  </si>
+  <si>
+    <t>5.7500</t>
+  </si>
+  <si>
+    <t>2.3000</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>NCP1117-3.3_SOT223</t>
+  </si>
+  <si>
+    <t>Regulator_Linear</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>SOT-223-3_TabPin2</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/AZ1117I.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AZ1117IH-3-3TRG1/5699672</t>
+  </si>
+  <si>
+    <t>104.8844</t>
+  </si>
+  <si>
+    <t>76.9444</t>
+  </si>
+  <si>
+    <t>8.3000</t>
+  </si>
+  <si>
+    <t>6.1000</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>RP2040</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>RP2040-QFN-56</t>
+  </si>
+  <si>
+    <t>https://datasheets.raspberrypi.com/rp2040/rp2040-datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/raspberry-pi/SC0914-13/14306010</t>
+  </si>
+  <si>
+    <t>89.3944</t>
+  </si>
+  <si>
+    <t>85.3944</t>
+  </si>
+  <si>
+    <t>7.7500</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>15-Mbps inverting photocouple,5 kVrms, 2.7 - 5.5 Vdd, push-pull output</t>
+  </si>
+  <si>
+    <t>TLP2761</t>
+  </si>
+  <si>
+    <t>Isolator</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>SO-6L_10x3.84mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>https://toshiba.semicon-storage.com/info/docget.jsp?did=28819&amp;prodName=TLP2761</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/toshiba-semiconductor-and-storage/TLP2761-TP-E/7809713</t>
+  </si>
+  <si>
+    <t>72.4560</t>
+  </si>
+  <si>
+    <t>91.7230</t>
+  </si>
+  <si>
+    <t>10.8000</t>
+  </si>
+  <si>
+    <t>3.3400</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>4-Channel ESD Protection for Super-Speed USB 3.0 Interface, USON-10</t>
+  </si>
+  <si>
+    <t>TPD4EUSB30</t>
+  </si>
+  <si>
+    <t>Power_Protection</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>USON-10_2.5x1.0mm_P0.5mm</t>
+  </si>
+  <si>
+    <t>Package_SON</t>
+  </si>
+  <si>
+    <t>http://www.ti.com/lit/ds/symlink/tpd2eusb30a.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/texas-instruments/TPD4EUSB30DQAR/2503665</t>
+  </si>
+  <si>
+    <t>7.0444</t>
+  </si>
+  <si>
+    <t>74.0444</t>
+  </si>
+  <si>
+    <t>1.3200</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>USB 2.0 Hi-Speed Hub Controller</t>
+  </si>
+  <si>
+    <t>USB2514B_Bi</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>QFN-36-1EP_6x6mm_P0.5mm_EP3.7x3.7mm</t>
+  </si>
+  <si>
+    <t>Package_DFN_QFN</t>
+  </si>
+  <si>
+    <t>http://ww1.microchip.com/downloads/en/DeviceDoc/00001692C.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/microchip-technology/USB2514B-I-M2/5639468</t>
+  </si>
+  <si>
+    <t>34.1844</t>
+  </si>
+  <si>
+    <t>85.0344</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>W25Q128JVS-Memory_Flash</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>W25Q128JVS</t>
+  </si>
+  <si>
+    <t>SOIC-8_5.23x5.23mm_P1.27mm</t>
+  </si>
+  <si>
+    <t>https://www.winbond.com/resource-files/w25q128jv%20revf%2003272018%20plus.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/winbond-electronics/W25Q128JVSIQ-TR/5803944</t>
+  </si>
+  <si>
+    <t>81.4944</t>
+  </si>
+  <si>
+    <t>78.5444</t>
+  </si>
+  <si>
+    <t>8.8000</t>
+  </si>
+  <si>
+    <t>4.4100</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>ABM8-272-T3</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>ABM8-272-T3_ABR</t>
+  </si>
+  <si>
+    <t>https://abracon.com/datasheets/ABM8-272-T3.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/abracon-llc/ABM8-272-T3/22472366</t>
+  </si>
+  <si>
+    <t>98.0476</t>
+  </si>
+  <si>
+    <t>76.8476</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Two pin crystal, small symbol</t>
+  </si>
+  <si>
+    <t>Crystal_Small</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>Crystal_SMD_5032-2Pin_5.0x3.2mm</t>
+  </si>
+  <si>
+    <t>Crystal</t>
+  </si>
+  <si>
+    <t>https://www.ctscorp.com/Files/DataSheets/Passives/FCP/Crystals/crystals-445-datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/en/products/detail/cts-frequency-controls/445C33D24M00000/3135787</t>
+  </si>
+  <si>
+    <t>49.0344</t>
+  </si>
+  <si>
+    <t>82.8744</t>
+  </si>
+  <si>
+    <t>5.7000</t>
+  </si>
+  <si>
+    <t>2.4000</t>
+  </si>
+  <si>
+    <t>KiBot Bill of Materials</t>
+  </si>
+  <si>
+    <t>Schematic:</t>
+  </si>
+  <si>
+    <t>pedalboard-hw</t>
+  </si>
+  <si>
+    <t>Variant:</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>Revision:</t>
+  </si>
+  <si>
+    <t>4.0.1-RC</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>KiCad Version:</t>
+  </si>
+  <si>
+    <t>10.0.1-10.0.1~ubuntu25.10.1</t>
+  </si>
+  <si>
+    <t>Component Groups:</t>
+  </si>
+  <si>
+    <t>Component Count:</t>
+  </si>
+  <si>
+    <t>138 (118 SMD/ 20 THT)</t>
+  </si>
+  <si>
+    <t>Fitted Components:</t>
+  </si>
+  <si>
+    <t>128 (115 SMD/ 13 THT)</t>
+  </si>
+  <si>
+    <t>Number of PCBs:</t>
+  </si>
+  <si>
+    <t>Total Components:</t>
+  </si>
+  <si>
+    <t>Barrel_Jack_Switch</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>Barrel_Jack_MountingPin</t>
+  </si>
+  <si>
+    <t>BarrelJack_Wuerth_6941xx301002</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (DNF)</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/6941xx301002.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/w%C3%BCrth-elektronik/694106301002/5047522</t>
+  </si>
+  <si>
+    <t>158.5316</t>
+  </si>
+  <si>
+    <t>100.6058</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>7.9000</t>
+  </si>
+  <si>
+    <t>5-pin DIN connector (5-pin DIN-5 stereo)</t>
+  </si>
+  <si>
+    <t>DIN-5_180degree</t>
+  </si>
+  <si>
+    <t>J2 J4</t>
+  </si>
+  <si>
+    <t>DIN5</t>
+  </si>
+  <si>
+    <t>CP-2350</t>
+  </si>
+  <si>
+    <t>https://www.switchcraft.com/assets/1/24/57PC5F_CD.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/switchcraft-inc/57PC5F/275385</t>
+  </si>
+  <si>
+    <t>71.9944</t>
+  </si>
+  <si>
+    <t>108.9944</t>
+  </si>
+  <si>
+    <t>17.5000</t>
+  </si>
+  <si>
+    <t>14.7500</t>
+  </si>
+  <si>
+    <t>J12 J16</t>
+  </si>
+  <si>
+    <t>Debug</t>
+  </si>
+  <si>
+    <t>PinHeader_1x03_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2.54mm</t>
+  </si>
+  <si>
+    <t>111.3094</t>
+  </si>
+  <si>
+    <t>86.5444</t>
   </si>
   <si>
     <t>1.7000</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>AP2553W6</t>
-  </si>
-  <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>SOT-23-6</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/AP255x.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/en/products/detail/AP2553W6-7/AP2553W6-7DICT-ND/3882112</t>
-  </si>
-  <si>
-    <t>55.0870</t>
-  </si>
-  <si>
-    <t>79.1174</t>
-  </si>
-  <si>
-    <t>3.6000</t>
-  </si>
-  <si>
-    <t>2.5000</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>AP64351</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>AP64501SP-13</t>
-  </si>
-  <si>
-    <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.71x3.4mm_ThermalVias</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/AP64501.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AP64501SP-13/10419715</t>
-  </si>
-  <si>
-    <t>141.5144</t>
-  </si>
-  <si>
-    <t>88.5944</t>
-  </si>
-  <si>
-    <t>6.9000</t>
-  </si>
-  <si>
-    <t>4.9000</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>I2C Serial EEPROM, 1Kb (128x8) with Unique Serial Number, SOT-23-5</t>
-  </si>
-  <si>
-    <t>AT24CS01-STUM</t>
-  </si>
-  <si>
-    <t>Memory_EEPROM</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
-    <t>http://ww1.microchip.com/downloads/en/DeviceDoc/Atmel-8815-SEEPROM-AT24CS01-02-Datasheet.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/microchip-technology/AT24CS01-STUM-T/3973063</t>
-  </si>
-  <si>
-    <t>127.9944</t>
-  </si>
-  <si>
-    <t>86.4944</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Low-Power, Two-Port, High-Speed, USB2.0 (480Mbps) or UART Switch, MSOP-10</t>
-  </si>
-  <si>
-    <t>FSUSB42MUX</t>
-  </si>
-  <si>
-    <t>Interface_USB</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>TSSOP-10_3x3mm_P0.5mm</t>
-  </si>
-  <si>
-    <t>Package_SO</t>
-  </si>
-  <si>
-    <t>https://www.onsemi.com/pub/Collateral/FSUSB42-D.PDF</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/onsemi/FSUSB42MUX/2036916</t>
-  </si>
-  <si>
-    <t>38.1144</t>
-  </si>
-  <si>
-    <t>73.8844</t>
-  </si>
-  <si>
-    <t>2.2500</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>NCP1117-3.3_SOT223</t>
-  </si>
-  <si>
-    <t>Regulator_Linear</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>SOT-223-3_TabPin2</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/AZ1117I.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AZ1117IH-3-3TRG1/5699672</t>
-  </si>
-  <si>
-    <t>104.8844</t>
-  </si>
-  <si>
-    <t>76.9444</t>
-  </si>
-  <si>
-    <t>8.3000</t>
-  </si>
-  <si>
-    <t>6.1000</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>RP2040</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>RP2040-QFN-56</t>
-  </si>
-  <si>
-    <t>https://datasheets.raspberrypi.com/rp2040/rp2040-datasheet.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/raspberry-pi/SC0914-13/14306010</t>
-  </si>
-  <si>
-    <t>89.3944</t>
-  </si>
-  <si>
-    <t>85.3944</t>
-  </si>
-  <si>
-    <t>7.7500</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>15-Mbps inverting photocouple,5 kVrms, 2.7 - 5.5 Vdd, push-pull output</t>
-  </si>
-  <si>
-    <t>TLP2761</t>
-  </si>
-  <si>
-    <t>Isolator</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>SO-6L_10x3.84mm_P1.27mm</t>
-  </si>
-  <si>
-    <t>https://toshiba.semicon-storage.com/info/docget.jsp?did=28819&amp;prodName=TLP2761</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/toshiba-semiconductor-and-storage/TLP2761-TP-E/7809713</t>
-  </si>
-  <si>
-    <t>72.4560</t>
-  </si>
-  <si>
-    <t>91.7230</t>
-  </si>
-  <si>
-    <t>10.8000</t>
-  </si>
-  <si>
-    <t>3.3400</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>4-Channel ESD Protection for Super-Speed USB 3.0 Interface, USON-10</t>
-  </si>
-  <si>
-    <t>TPD4EUSB30</t>
-  </si>
-  <si>
-    <t>Power_Protection</t>
-  </si>
-  <si>
-    <t>U11</t>
-  </si>
-  <si>
-    <t>USON-10_2.5x1.0mm_P0.5mm</t>
-  </si>
-  <si>
-    <t>Package_SON</t>
-  </si>
-  <si>
-    <t>http://www.ti.com/lit/ds/symlink/tpd2eusb30a.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/texas-instruments/TPD4EUSB30DQAR/2503665</t>
-  </si>
-  <si>
-    <t>7.0444</t>
-  </si>
-  <si>
-    <t>74.0444</t>
-  </si>
-  <si>
-    <t>1.3200</t>
-  </si>
-  <si>
-    <t>2.3000</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>USB 2.0 Hi-Speed Hub Controller</t>
-  </si>
-  <si>
-    <t>USB2514B_Bi</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>QFN-36-1EP_6x6mm_P0.5mm_EP3.7x3.7mm</t>
-  </si>
-  <si>
-    <t>Package_DFN_QFN</t>
-  </si>
-  <si>
-    <t>http://ww1.microchip.com/downloads/en/DeviceDoc/00001692C.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/microchip-technology/USB2514B-I-M2/5639468</t>
-  </si>
-  <si>
-    <t>34.1844</t>
-  </si>
-  <si>
-    <t>85.0344</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>W25Q128JVS-Memory_Flash</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>W25Q128JVS</t>
-  </si>
-  <si>
-    <t>SOIC-8_5.23x5.23mm_P1.27mm</t>
-  </si>
-  <si>
-    <t>https://www.winbond.com/resource-files/w25q128jv%20revf%2003272018%20plus.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/winbond-electronics/W25Q128JVSIQ-TR/5803944</t>
-  </si>
-  <si>
-    <t>81.4944</t>
-  </si>
-  <si>
-    <t>78.5444</t>
-  </si>
-  <si>
-    <t>8.8000</t>
-  </si>
-  <si>
-    <t>4.4100</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>ABM8-272-T3</t>
-  </si>
-  <si>
-    <t>Y2</t>
-  </si>
-  <si>
-    <t>ABM8-272-T3_ABR</t>
-  </si>
-  <si>
-    <t>https://abracon.com/datasheets/ABM8-272-T3.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/abracon-llc/ABM8-272-T3/22472366</t>
-  </si>
-  <si>
-    <t>97.9944</t>
-  </si>
-  <si>
-    <t>76.9067</t>
-  </si>
-  <si>
-    <t>2.7000</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>Two pin crystal, small symbol</t>
-  </si>
-  <si>
-    <t>Crystal_Small</t>
-  </si>
-  <si>
-    <t>Y1</t>
-  </si>
-  <si>
-    <t>Crystal_SMD_5032-2Pin_5.0x3.2mm</t>
-  </si>
-  <si>
-    <t>Crystal</t>
-  </si>
-  <si>
-    <t>https://www.ctscorp.com/Files/DataSheets/Passives/FCP/Crystals/crystals-445-datasheet.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/en/products/detail/cts-frequency-controls/445C33D24M00000/3135787</t>
-  </si>
-  <si>
-    <t>48.8344</t>
-  </si>
-  <si>
-    <t>82.8744</t>
-  </si>
-  <si>
-    <t>5.7000</t>
-  </si>
-  <si>
-    <t>2.4000</t>
-  </si>
-  <si>
-    <t>KiBot Bill of Materials</t>
-  </si>
-  <si>
-    <t>Schematic:</t>
-  </si>
-  <si>
-    <t>pedalboard-hw</t>
-  </si>
-  <si>
-    <t>Variant:</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>Revision:</t>
-  </si>
-  <si>
-    <t>4.0.1-RC</t>
-  </si>
-  <si>
-    <t>Date:</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>KiCad Version:</t>
-  </si>
-  <si>
-    <t>9.0.7+1</t>
-  </si>
-  <si>
-    <t>Component Groups:</t>
-  </si>
-  <si>
-    <t>Component Count:</t>
-  </si>
-  <si>
-    <t>138 (118 SMD/ 20 THT)</t>
-  </si>
-  <si>
-    <t>Fitted Components:</t>
-  </si>
-  <si>
-    <t>128 (115 SMD/ 13 THT)</t>
-  </si>
-  <si>
-    <t>Number of PCBs:</t>
-  </si>
-  <si>
-    <t>Total Components:</t>
-  </si>
-  <si>
-    <t>Barrel_Jack_Switch</t>
-  </si>
-  <si>
-    <t>J7</t>
-  </si>
-  <si>
-    <t>Barrel_Jack_MountingPin</t>
-  </si>
-  <si>
-    <t>BarrelJack_Wuerth_6941xx301002</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (DNF)</t>
-  </si>
-  <si>
-    <t>https://www.we-online.com/components/products/datasheet/6941xx301002.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/w%C3%BCrth-elektronik/694106301002/5047522</t>
-  </si>
-  <si>
-    <t>158.5316</t>
-  </si>
-  <si>
-    <t>100.6058</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>7.9000</t>
-  </si>
-  <si>
-    <t>5-pin DIN connector (5-pin DIN-5 stereo)</t>
-  </si>
-  <si>
-    <t>DIN-5_180degree</t>
-  </si>
-  <si>
-    <t>J2 J4</t>
-  </si>
-  <si>
-    <t>DIN5</t>
-  </si>
-  <si>
-    <t>CP-2350</t>
-  </si>
-  <si>
-    <t>https://www.switchcraft.com/assets/1/24/57PC5F_CD.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/switchcraft-inc/57PC5F/275385</t>
-  </si>
-  <si>
-    <t>71.9944</t>
-  </si>
-  <si>
-    <t>108.9944</t>
-  </si>
-  <si>
-    <t>17.5000</t>
-  </si>
-  <si>
-    <t>14.7500</t>
-  </si>
-  <si>
-    <t>J12 J16</t>
-  </si>
-  <si>
-    <t>Debug</t>
-  </si>
-  <si>
-    <t>PinHeader_1x03_P2.54mm_Vertical</t>
-  </si>
-  <si>
-    <t>Connector_PinHeader_2.54mm</t>
-  </si>
-  <si>
-    <t>111.3094</t>
-  </si>
-  <si>
-    <t>86.5444</t>
   </si>
   <si>
     <t>6.7800</t>
@@ -2323,7 +2314,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="60.7109375" customWidth="1"/>
     <col min="6" max="6" width="25.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -2343,7 +2334,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2368,13 +2359,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="C2" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F2" s="3">
         <v>55</v>
@@ -2382,41 +2373,41 @@
     </row>
     <row r="3" spans="1:23">
       <c r="C3" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="C4" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="C5" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -2424,13 +2415,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="C6" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F6" s="3">
         <v>128</v>
@@ -3181,10 +3172,10 @@
         <v>32</v>
       </c>
       <c r="L18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>112</v>
@@ -3193,10 +3184,10 @@
         <v>66</v>
       </c>
       <c r="P18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q18" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="R18" s="11" t="s">
         <v>77</v>
@@ -3211,15 +3202,15 @@
         <v>42</v>
       </c>
       <c r="V18" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W18" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="W18" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="30" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>118</v>
@@ -3231,10 +3222,10 @@
         <v>26</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>132</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>122</v>
@@ -3252,10 +3243,10 @@
         <v>32</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>35</v>
@@ -3264,10 +3255,10 @@
         <v>36</v>
       </c>
       <c r="P19" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q19" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>135</v>
       </c>
       <c r="R19" s="7" t="s">
         <v>39</v>
@@ -3282,36 +3273,36 @@
         <v>42</v>
       </c>
       <c r="V19" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W19" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W19" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="30" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="H20" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>23</v>
@@ -3323,10 +3314,10 @@
         <v>32</v>
       </c>
       <c r="L20" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>144</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>35</v>
@@ -3335,10 +3326,10 @@
         <v>66</v>
       </c>
       <c r="P20" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q20" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="Q20" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="R20" s="11" t="s">
         <v>77</v>
@@ -3353,36 +3344,36 @@
         <v>42</v>
       </c>
       <c r="V20" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="W20" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>23</v>
@@ -3394,10 +3385,10 @@
         <v>32</v>
       </c>
       <c r="L21" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>58</v>
@@ -3406,10 +3397,10 @@
         <v>66</v>
       </c>
       <c r="P21" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q21" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="R21" s="7" t="s">
         <v>39</v>
@@ -3424,33 +3415,33 @@
         <v>42</v>
       </c>
       <c r="V21" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="W21" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="W21" s="7" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="30" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>109</v>
@@ -3465,22 +3456,22 @@
         <v>32</v>
       </c>
       <c r="L22" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="M22" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="N22" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P22" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q22" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="Q22" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>51</v>
@@ -3495,33 +3486,33 @@
         <v>42</v>
       </c>
       <c r="V22" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="W22" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="30" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>109</v>
@@ -3536,10 +3527,10 @@
         <v>32</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>35</v>
@@ -3548,10 +3539,10 @@
         <v>66</v>
       </c>
       <c r="P23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q23" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="R23" s="7" t="s">
         <v>51</v>
@@ -3566,33 +3557,33 @@
         <v>42</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W23" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>188</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>109</v>
@@ -3607,10 +3598,10 @@
         <v>32</v>
       </c>
       <c r="L24" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="M24" s="12" t="s">
         <v>189</v>
-      </c>
-      <c r="M24" s="12" t="s">
-        <v>190</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>35</v>
@@ -3619,10 +3610,10 @@
         <v>36</v>
       </c>
       <c r="P24" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q24" s="11" t="s">
         <v>191</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>192</v>
       </c>
       <c r="R24" s="11" t="s">
         <v>39</v>
@@ -3631,16 +3622,16 @@
         <v>40</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V24" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="W24" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="30" customHeight="1">
@@ -3651,19 +3642,19 @@
         <v>24</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>198</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>199</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>109</v>
@@ -3678,63 +3669,63 @@
         <v>32</v>
       </c>
       <c r="L25" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>201</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="O25" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="P25" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="Q25" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="Q25" s="7" t="s">
+      <c r="R25" s="7" t="s">
         <v>204</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>205</v>
       </c>
       <c r="S25" s="7" t="s">
         <v>40</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U25" s="7" t="s">
         <v>42</v>
       </c>
       <c r="V25" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="W25" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="W25" s="7" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E26" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="G26" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>212</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>109</v>
@@ -3749,7 +3740,7 @@
         <v>32</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>24</v>
@@ -3761,54 +3752,54 @@
         <v>66</v>
       </c>
       <c r="P26" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q26" s="11" t="s">
         <v>213</v>
-      </c>
-      <c r="Q26" s="11" t="s">
-        <v>214</v>
       </c>
       <c r="R26" s="11" t="s">
         <v>39</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U26" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V26" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="W26" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="W26" s="11" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="30" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="H27" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>23</v>
@@ -3820,10 +3811,10 @@
         <v>32</v>
       </c>
       <c r="L27" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="M27" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>224</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>58</v>
@@ -3832,10 +3823,10 @@
         <v>66</v>
       </c>
       <c r="P27" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q27" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>226</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>51</v>
@@ -3844,42 +3835,42 @@
         <v>40</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U27" s="7" t="s">
         <v>42</v>
       </c>
       <c r="V27" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="W27" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="W27" s="7" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="30" customHeight="1">
       <c r="A28" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" s="11" t="s">
+      <c r="F28" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="G28" s="11" t="s">
+      <c r="H28" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>234</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>23</v>
@@ -3891,10 +3882,10 @@
         <v>32</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="N28" s="11" t="s">
         <v>48</v>
@@ -3903,10 +3894,10 @@
         <v>66</v>
       </c>
       <c r="P28" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>39</v>
@@ -3915,39 +3906,39 @@
         <v>40</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U28" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="30" customHeight="1">
       <c r="A29" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="D29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="F29" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>109</v>
@@ -3962,10 +3953,10 @@
         <v>32</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>48</v>
@@ -3974,10 +3965,10 @@
         <v>66</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="R29" s="7" t="s">
         <v>77</v>
@@ -3992,10 +3983,10 @@
         <v>42</v>
       </c>
       <c r="V29" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="W29" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="30" customHeight="1">
@@ -4006,22 +3997,22 @@
         <v>24</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>55</v>
@@ -4033,10 +4024,10 @@
         <v>32</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N30" s="11" t="s">
         <v>35</v>
@@ -4045,13 +4036,13 @@
         <v>59</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S30" s="11" t="s">
         <v>40</v>
@@ -4063,36 +4054,36 @@
         <v>42</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="30" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>23</v>
@@ -4104,10 +4095,10 @@
         <v>32</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N31" s="7" t="s">
         <v>58</v>
@@ -4116,10 +4107,10 @@
         <v>66</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="R31" s="7" t="s">
         <v>77</v>
@@ -4134,33 +4125,33 @@
         <v>42</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W31" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="30" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>109</v>
@@ -4175,10 +4166,10 @@
         <v>32</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="N32" s="11" t="s">
         <v>58</v>
@@ -4187,13 +4178,13 @@
         <v>66</v>
       </c>
       <c r="P32" s="11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>40</v>
@@ -4205,36 +4196,36 @@
         <v>42</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="1:23" ht="30" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>289</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>31</v>
@@ -4246,10 +4237,10 @@
         <v>32</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N33" s="7" t="s">
         <v>35</v>
@@ -4258,13 +4249,13 @@
         <v>36</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S33" s="7" t="s">
         <v>40</v>
@@ -4276,36 +4267,36 @@
         <v>42</v>
       </c>
       <c r="V33" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W33" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W33" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:23" ht="30" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>31</v>
@@ -4317,10 +4308,10 @@
         <v>32</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N34" s="11" t="s">
         <v>35</v>
@@ -4329,13 +4320,13 @@
         <v>36</v>
       </c>
       <c r="P34" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q34" s="11" t="s">
         <v>50</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S34" s="11" t="s">
         <v>40</v>
@@ -4347,36 +4338,36 @@
         <v>42</v>
       </c>
       <c r="V34" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W34" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="W34" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="30" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>23</v>
@@ -4388,10 +4379,10 @@
         <v>32</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N35" s="7" t="s">
         <v>35</v>
@@ -4400,10 +4391,10 @@
         <v>66</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="R35" s="7" t="s">
         <v>39</v>
@@ -4418,36 +4409,36 @@
         <v>42</v>
       </c>
       <c r="V35" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W35" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W35" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:23" ht="30" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>52</v>
@@ -4459,22 +4450,22 @@
         <v>32</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="N36" s="11" t="s">
         <v>35</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P36" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R36" s="11" t="s">
         <v>51</v>
@@ -4489,36 +4480,36 @@
         <v>42</v>
       </c>
       <c r="V36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W36" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="W36" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:23" ht="30" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>69</v>
@@ -4530,22 +4521,22 @@
         <v>32</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N37" s="7" t="s">
         <v>35</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="R37" s="7" t="s">
         <v>51</v>
@@ -4560,36 +4551,36 @@
         <v>42</v>
       </c>
       <c r="V37" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W37" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W37" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:23" ht="30" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>69</v>
@@ -4601,22 +4592,22 @@
         <v>32</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N38" s="11" t="s">
         <v>58</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P38" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="R38" s="11" t="s">
         <v>51</v>
@@ -4631,36 +4622,36 @@
         <v>42</v>
       </c>
       <c r="V38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W38" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="W38" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="30" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>31</v>
@@ -4672,10 +4663,10 @@
         <v>32</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="N39" s="7" t="s">
         <v>35</v>
@@ -4684,10 +4675,10 @@
         <v>36</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="R39" s="7" t="s">
         <v>39</v>
@@ -4702,36 +4693,36 @@
         <v>42</v>
       </c>
       <c r="V39" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W39" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="30" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>31</v>
@@ -4743,10 +4734,10 @@
         <v>32</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N40" s="11" t="s">
         <v>58</v>
@@ -4755,10 +4746,10 @@
         <v>36</v>
       </c>
       <c r="P40" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="R40" s="11" t="s">
         <v>51</v>
@@ -4773,36 +4764,36 @@
         <v>42</v>
       </c>
       <c r="V40" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W40" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="W40" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="30" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>23</v>
@@ -4814,10 +4805,10 @@
         <v>32</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="N41" s="7" t="s">
         <v>58</v>
@@ -4826,10 +4817,10 @@
         <v>66</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="R41" s="7" t="s">
         <v>77</v>
@@ -4844,36 +4835,36 @@
         <v>42</v>
       </c>
       <c r="V41" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W41" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W41" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:23" ht="30" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>69</v>
@@ -4885,22 +4876,22 @@
         <v>32</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M42" s="12" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P42" s="11" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Q42" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="R42" s="11" t="s">
         <v>77</v>
@@ -4915,33 +4906,33 @@
         <v>42</v>
       </c>
       <c r="V42" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="W42" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="W42" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:23" ht="30" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>109</v>
@@ -4956,10 +4947,10 @@
         <v>32</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="N43" s="7" t="s">
         <v>35</v>
@@ -4968,51 +4959,51 @@
         <v>36</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S43" s="7" t="s">
         <v>40</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U43" s="7" t="s">
         <v>42</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="W43" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:23" ht="30" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="G44" s="11" t="s">
         <v>358</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>361</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>109</v>
@@ -5027,25 +5018,25 @@
         <v>32</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="N44" s="11" t="s">
         <v>35</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P44" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="Q44" s="11" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="R44" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S44" s="11" t="s">
         <v>40</v>
@@ -5057,36 +5048,36 @@
         <v>42</v>
       </c>
       <c r="V44" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="W44" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="1:23" ht="30" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F45" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>372</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>31</v>
@@ -5098,25 +5089,25 @@
         <v>32</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O45" s="5" t="s">
         <v>36</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>40</v>
@@ -5128,36 +5119,36 @@
         <v>42</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:23" ht="30" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>23</v>
@@ -5169,10 +5160,10 @@
         <v>32</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>48</v>
@@ -5181,10 +5172,10 @@
         <v>66</v>
       </c>
       <c r="P46" s="11" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="Q46" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>51</v>
@@ -5199,33 +5190,33 @@
         <v>42</v>
       </c>
       <c r="V46" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="W46" s="11" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="45" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>109</v>
@@ -5240,10 +5231,10 @@
         <v>32</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="N47" s="7" t="s">
         <v>58</v>
@@ -5252,10 +5243,10 @@
         <v>66</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>77</v>
@@ -5270,36 +5261,36 @@
         <v>42</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="W47" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" spans="1:23" ht="30" customHeight="1">
       <c r="A48" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="E48" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="F48" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="G48" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="G48" s="11" t="s">
-        <v>405</v>
-      </c>
       <c r="H48" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>23</v>
@@ -5311,10 +5302,10 @@
         <v>32</v>
       </c>
       <c r="L48" s="11" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="N48" s="11" t="s">
         <v>35</v>
@@ -5323,10 +5314,10 @@
         <v>66</v>
       </c>
       <c r="P48" s="11" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="Q48" s="11" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="R48" s="11" t="s">
         <v>39</v>
@@ -5341,36 +5332,36 @@
         <v>42</v>
       </c>
       <c r="V48" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="W48" s="11" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:23" ht="30" customHeight="1">
       <c r="A49" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="E49" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="F49" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="H49" s="7" t="s">
         <v>413</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>416</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>23</v>
@@ -5382,10 +5373,10 @@
         <v>32</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N49" s="7" t="s">
         <v>48</v>
@@ -5394,10 +5385,10 @@
         <v>66</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="R49" s="7" t="s">
         <v>39</v>
@@ -5412,36 +5403,36 @@
         <v>42</v>
       </c>
       <c r="V49" s="7" t="s">
-        <v>159</v>
+        <v>418</v>
       </c>
       <c r="W49" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="30" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="E50" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="F50" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="G50" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="E50" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>423</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>426</v>
-      </c>
       <c r="H50" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>23</v>
@@ -5453,10 +5444,10 @@
         <v>32</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N50" s="11" t="s">
         <v>58</v>
@@ -5465,10 +5456,10 @@
         <v>66</v>
       </c>
       <c r="P50" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q50" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="R50" s="11" t="s">
         <v>39</v>
@@ -5483,33 +5474,33 @@
         <v>42</v>
       </c>
       <c r="V50" s="11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="W50" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" spans="1:23" ht="30" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F51" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G51" s="7" t="s">
         <v>434</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>436</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>109</v>
@@ -5524,10 +5515,10 @@
         <v>32</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N51" s="7" t="s">
         <v>35</v>
@@ -5536,10 +5527,10 @@
         <v>66</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>51</v>
@@ -5554,36 +5545,36 @@
         <v>42</v>
       </c>
       <c r="V51" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="W51" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="30" customHeight="1">
       <c r="A52" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="E52" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="F52" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="G52" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="E52" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>444</v>
-      </c>
-      <c r="G52" s="11" t="s">
-        <v>447</v>
-      </c>
       <c r="H52" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>23</v>
@@ -5595,10 +5586,10 @@
         <v>32</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N52" s="11" t="s">
         <v>35</v>
@@ -5607,13 +5598,13 @@
         <v>66</v>
       </c>
       <c r="P52" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="Q52" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="R52" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S52" s="11" t="s">
         <v>40</v>
@@ -5625,36 +5616,36 @@
         <v>42</v>
       </c>
       <c r="V52" s="11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="W52" s="11" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:23" ht="30" customHeight="1">
       <c r="A53" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="D53" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="E53" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="F53" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="H53" s="7" t="s">
         <v>458</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>460</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>23</v>
@@ -5666,10 +5657,10 @@
         <v>32</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N53" s="7" t="s">
         <v>48</v>
@@ -5678,10 +5669,10 @@
         <v>66</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>39</v>
@@ -5696,36 +5687,36 @@
         <v>42</v>
       </c>
       <c r="V53" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="W53" s="7" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:23" ht="30" customHeight="1">
       <c r="A54" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="E54" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="F54" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="G54" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="H54" s="11" t="s">
         <v>469</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>472</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>23</v>
@@ -5737,10 +5728,10 @@
         <v>32</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N54" s="11" t="s">
         <v>48</v>
@@ -5749,10 +5740,10 @@
         <v>66</v>
       </c>
       <c r="P54" s="11" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Q54" s="11" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="R54" s="11" t="s">
         <v>77</v>
@@ -5767,33 +5758,33 @@
         <v>42</v>
       </c>
       <c r="V54" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W54" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:23" ht="30" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>109</v>
@@ -5808,10 +5799,10 @@
         <v>32</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="N55" s="7" t="s">
         <v>35</v>
@@ -5820,10 +5811,10 @@
         <v>66</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="R55" s="7" t="s">
         <v>51</v>
@@ -5838,33 +5829,33 @@
         <v>42</v>
       </c>
       <c r="V55" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="W55" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="30" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H56" s="11" t="s">
         <v>109</v>
@@ -5879,10 +5870,10 @@
         <v>32</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N56" s="11" t="s">
         <v>35</v>
@@ -5891,10 +5882,10 @@
         <v>66</v>
       </c>
       <c r="P56" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="Q56" s="11" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="R56" s="11" t="s">
         <v>51</v>
@@ -5909,36 +5900,36 @@
         <v>42</v>
       </c>
       <c r="V56" s="11" t="s">
-        <v>496</v>
+        <v>374</v>
       </c>
       <c r="W56" s="11" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="30" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>23</v>
@@ -5950,10 +5941,10 @@
         <v>32</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="N57" s="7" t="s">
         <v>48</v>
@@ -5962,10 +5953,10 @@
         <v>66</v>
       </c>
       <c r="P57" s="7" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="R57" s="7" t="s">
         <v>77</v>
@@ -5980,10 +5971,10 @@
         <v>42</v>
       </c>
       <c r="V57" s="7" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="W57" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -6004,7 +5995,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="45.7109375" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="28.7109375" customWidth="1"/>
     <col min="7" max="7" width="42.7109375" customWidth="1"/>
@@ -6023,7 +6014,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -6048,13 +6039,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="C2" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F2" s="3">
         <v>55</v>
@@ -6062,41 +6053,41 @@
     </row>
     <row r="3" spans="1:23">
       <c r="C3" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="C4" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="C5" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -6104,13 +6095,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="C6" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F6" s="3">
         <v>128</v>
@@ -6195,19 +6186,19 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>109</v>
@@ -6216,16 +6207,16 @@
         <v>23</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>58</v>
@@ -6234,10 +6225,10 @@
         <v>66</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="R9" s="7" t="s">
         <v>39</v>
@@ -6246,16 +6237,16 @@
         <v>40</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="30" customHeight="1">
@@ -6263,22 +6254,22 @@
         <v>31</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>539</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>542</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>543</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>109</v>
@@ -6287,16 +6278,16 @@
         <v>31</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="N10" s="11" t="s">
         <v>35</v>
@@ -6305,10 +6296,10 @@
         <v>36</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="R10" s="11" t="s">
         <v>39</v>
@@ -6317,16 +6308,16 @@
         <v>40</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -6337,34 +6328,34 @@
         <v>24</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>163</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>24</v>
@@ -6376,10 +6367,10 @@
         <v>36</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>51</v>
@@ -6388,16 +6379,16 @@
         <v>40</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="30" customHeight="1">
@@ -6408,37 +6399,37 @@
         <v>24</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>163</v>
-      </c>
       <c r="E12" s="11" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>35</v>
@@ -6447,28 +6438,28 @@
         <v>36</v>
       </c>
       <c r="P12" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="W12" s="11" t="s">
         <v>561</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="R12" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="S12" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="T12" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="U12" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="V12" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="W12" s="11" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -6476,37 +6467,37 @@
         <v>69</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>24</v>
@@ -6518,13 +6509,13 @@
         <v>66</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>40</v>
@@ -6533,13 +6524,13 @@
         <v>41</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="V13" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="W13" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="W13" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="30" customHeight="1">
@@ -6550,37 +6541,37 @@
         <v>24</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>569</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>572</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N14" s="11" t="s">
         <v>35</v>
@@ -6589,10 +6580,10 @@
         <v>36</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="R14" s="11" t="s">
         <v>51</v>
@@ -6604,13 +6595,13 @@
         <v>41</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>378</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -6633,27 +6624,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
